--- a/144/DQ Templates and Instructions/Topic 4 DQ 2/Topic 4 DQ 2.xlsx
+++ b/144/DQ Templates and Instructions/Topic 4 DQ 2/Topic 4 DQ 2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gcumail.sharepoint.com/sites/MathematicsProgramFacultyStaff-MATOFTF/Shared Documents/MATOFTF/ALEKS/DQ Templates and Instructions/Topic 4 DQ 2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="620" documentId="8_{C5F6D942-BE47-4B16-B7DF-0F8A5C8F158C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7BBECDCF-CCC7-4EFB-BFBF-58ED0EFFAB18}"/>
+  <xr:revisionPtr revIDLastSave="627" documentId="8_{C5F6D942-BE47-4B16-B7DF-0F8A5C8F158C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83675C0D-D250-4902-9B49-D52F8AAAEA40}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4FCF7FA6-22BB-4545-AB27-D5B8AACA448D}"/>
+    <workbookView xWindow="1470" yWindow="1470" windowWidth="21600" windowHeight="11295" xr2:uid="{4FCF7FA6-22BB-4545-AB27-D5B8AACA448D}"/>
   </bookViews>
   <sheets>
     <sheet name="Goals and Instructions" sheetId="5" r:id="rId1"/>
@@ -1098,7 +1098,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="167">
+  <cellXfs count="165">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1320,6 +1320,118 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
@@ -1424,133 +1536,14 @@
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1561,9 +1554,6 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1635,9 +1625,6 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1650,9 +1637,6 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1679,6 +1663,14 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2960,7 +2952,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7870B2E2-92BC-47AC-B93B-26715350F717}">
-  <dimension ref="B2:K22"/>
+  <dimension ref="B2:K23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3.7109375" style="16" customWidth="1"/>
@@ -2982,10 +2974,10 @@
       <c r="C2" s="33" t="s">
         <v>100</v>
       </c>
-      <c r="D2" s="97" t="s">
+      <c r="D2" s="67" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="98"/>
+      <c r="E2" s="68"/>
       <c r="H2" s="16"/>
       <c r="I2" s="16"/>
     </row>
@@ -3006,18 +2998,18 @@
       <c r="I4" s="16"/>
     </row>
     <row r="5" spans="2:10" ht="16.5" thickTop="1">
-      <c r="B5" s="103" t="s">
+      <c r="B5" s="73" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="104"/>
+      <c r="C5" s="74"/>
       <c r="D5" s="16"/>
       <c r="E5" s="19">
         <v>15</v>
       </c>
-      <c r="F5" s="117" t="s">
+      <c r="F5" s="87" t="s">
         <v>93</v>
       </c>
-      <c r="G5" s="118"/>
+      <c r="G5" s="88"/>
       <c r="H5" s="20"/>
       <c r="I5" s="20"/>
     </row>
@@ -3032,10 +3024,10 @@
       <c r="E6" s="21">
         <v>15</v>
       </c>
-      <c r="F6" s="119" t="s">
+      <c r="F6" s="89" t="s">
         <v>94</v>
       </c>
-      <c r="G6" s="120"/>
+      <c r="G6" s="90"/>
       <c r="H6" s="22"/>
       <c r="I6" s="22"/>
     </row>
@@ -3050,10 +3042,10 @@
       <c r="E7" s="23">
         <v>16</v>
       </c>
-      <c r="F7" s="121" t="s">
+      <c r="F7" s="91" t="s">
         <v>95</v>
       </c>
-      <c r="G7" s="122"/>
+      <c r="G7" s="92"/>
       <c r="H7" s="20"/>
       <c r="I7" s="20"/>
     </row>
@@ -3068,10 +3060,10 @@
       <c r="E8" s="24">
         <v>16</v>
       </c>
-      <c r="F8" s="123" t="s">
+      <c r="F8" s="93" t="s">
         <v>96</v>
       </c>
-      <c r="G8" s="124"/>
+      <c r="G8" s="94"/>
       <c r="H8" s="22"/>
       <c r="I8" s="22"/>
     </row>
@@ -3084,11 +3076,11 @@
       </c>
       <c r="D9" s="16"/>
       <c r="E9" s="16"/>
-      <c r="F9" s="70" t="s">
+      <c r="F9" s="98" t="s">
         <v>18</v>
       </c>
-      <c r="G9" s="70"/>
-      <c r="H9" s="70"/>
+      <c r="G9" s="98"/>
+      <c r="H9" s="98"/>
       <c r="I9" s="16"/>
     </row>
     <row r="10" spans="2:10" ht="16.5" thickBot="1">
@@ -3105,37 +3097,37 @@
     </row>
     <row r="11" spans="2:10" ht="16.5" thickTop="1" thickBot="1"/>
     <row r="12" spans="2:10" ht="14.45" customHeight="1">
-      <c r="B12" s="105" t="s">
+      <c r="B12" s="75" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="106"/>
-      <c r="D12" s="106"/>
-      <c r="E12" s="106"/>
-      <c r="F12" s="107"/>
+      <c r="C12" s="76"/>
+      <c r="D12" s="76"/>
+      <c r="E12" s="76"/>
+      <c r="F12" s="77"/>
     </row>
     <row r="13" spans="2:10" ht="15.75" thickBot="1">
-      <c r="B13" s="108"/>
-      <c r="C13" s="109"/>
-      <c r="D13" s="109"/>
-      <c r="E13" s="109"/>
-      <c r="F13" s="110"/>
+      <c r="B13" s="78"/>
+      <c r="C13" s="79"/>
+      <c r="D13" s="79"/>
+      <c r="E13" s="79"/>
+      <c r="F13" s="80"/>
       <c r="J13" s="26"/>
     </row>
     <row r="14" spans="2:10" ht="16.899999999999999" customHeight="1">
-      <c r="B14" s="111" t="s">
+      <c r="B14" s="81" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="112"/>
-      <c r="D14" s="112"/>
-      <c r="E14" s="112"/>
-      <c r="F14" s="113"/>
+      <c r="C14" s="82"/>
+      <c r="D14" s="82"/>
+      <c r="E14" s="82"/>
+      <c r="F14" s="83"/>
     </row>
     <row r="15" spans="2:10" ht="16.899999999999999" customHeight="1" thickBot="1">
-      <c r="B15" s="114"/>
-      <c r="C15" s="115"/>
-      <c r="D15" s="115"/>
-      <c r="E15" s="115"/>
-      <c r="F15" s="116"/>
+      <c r="B15" s="84"/>
+      <c r="C15" s="85"/>
+      <c r="D15" s="85"/>
+      <c r="E15" s="85"/>
+      <c r="F15" s="86"/>
     </row>
     <row r="16" spans="2:10">
       <c r="B16" s="27" t="s">
@@ -3150,37 +3142,37 @@
       <c r="E16" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="F16" s="101" t="s">
+      <c r="F16" s="71" t="s">
         <v>26</v>
       </c>
-      <c r="G16" s="101" t="s">
+      <c r="G16" s="71" t="s">
         <v>27</v>
       </c>
-      <c r="H16" s="99" t="s">
+      <c r="H16" s="69" t="s">
         <v>28</v>
       </c>
-      <c r="I16" s="85"/>
+      <c r="I16" s="113"/>
     </row>
     <row r="17" spans="2:11" ht="15.75" thickBot="1">
       <c r="B17" s="56"/>
       <c r="C17" s="57"/>
       <c r="D17" s="57"/>
       <c r="E17" s="57"/>
-      <c r="F17" s="102"/>
-      <c r="G17" s="102"/>
-      <c r="H17" s="100"/>
-      <c r="I17" s="85"/>
+      <c r="F17" s="72"/>
+      <c r="G17" s="72"/>
+      <c r="H17" s="70"/>
+      <c r="I17" s="113"/>
     </row>
     <row r="18" spans="2:11" ht="14.45" customHeight="1">
-      <c r="B18" s="76" t="str">
+      <c r="B18" s="104" t="str">
         <f ca="1">IF(C2="Your Name Here!", "Enter your name in C2 and your very own problem will appear here:)","Compute the monthly payments to pay back a loan of $"&amp;Random!H19&amp;" in "&amp;Random!H20&amp;" years an APR of "&amp;Random!H21&amp;"% compounded monthly. Find the total amount payed on the loan and the interest payed.")</f>
         <v>Compute the monthly payments to pay back a loan of $2200 in 5 years an APR of 20.29% compounded monthly. Find the total amount payed on the loan and the interest payed.</v>
       </c>
-      <c r="C18" s="77"/>
-      <c r="D18" s="77"/>
-      <c r="E18" s="78"/>
-      <c r="F18" s="71"/>
-      <c r="G18" s="90" t="s">
+      <c r="C18" s="105"/>
+      <c r="D18" s="105"/>
+      <c r="E18" s="106"/>
+      <c r="F18" s="99"/>
+      <c r="G18" s="118" t="s">
         <v>97</v>
       </c>
       <c r="H18" s="29" t="s">
@@ -3195,49 +3187,63 @@
       <c r="K18" s="26"/>
     </row>
     <row r="19" spans="2:11">
-      <c r="B19" s="79"/>
-      <c r="C19" s="80"/>
-      <c r="D19" s="80"/>
-      <c r="E19" s="81"/>
-      <c r="F19" s="72"/>
-      <c r="G19" s="91"/>
-      <c r="H19" s="86"/>
-      <c r="I19" s="88"/>
-      <c r="J19" s="74"/>
+      <c r="B19" s="107"/>
+      <c r="C19" s="108"/>
+      <c r="D19" s="108"/>
+      <c r="E19" s="109"/>
+      <c r="F19" s="100"/>
+      <c r="G19" s="119"/>
+      <c r="H19" s="114"/>
+      <c r="I19" s="116"/>
+      <c r="J19" s="102"/>
       <c r="K19" s="26"/>
     </row>
     <row r="20" spans="2:11" ht="24" customHeight="1" thickBot="1">
-      <c r="B20" s="82"/>
-      <c r="C20" s="83"/>
-      <c r="D20" s="83"/>
-      <c r="E20" s="84"/>
-      <c r="F20" s="73"/>
-      <c r="G20" s="92"/>
-      <c r="H20" s="87"/>
-      <c r="I20" s="89"/>
-      <c r="J20" s="75"/>
+      <c r="B20" s="110"/>
+      <c r="C20" s="111"/>
+      <c r="D20" s="111"/>
+      <c r="E20" s="112"/>
+      <c r="F20" s="101"/>
+      <c r="G20" s="120"/>
+      <c r="H20" s="115"/>
+      <c r="I20" s="117"/>
+      <c r="J20" s="103"/>
       <c r="K20" s="26"/>
     </row>
-    <row r="21" spans="2:11" ht="15.75" thickBot="1">
+    <row r="21" spans="2:11" ht="15.75" customHeight="1" thickBot="1">
       <c r="B21" s="32"/>
-      <c r="F21" s="93" t="s">
+      <c r="F21" s="163" t="s">
         <v>92</v>
       </c>
-      <c r="G21" s="94"/>
-      <c r="H21" s="67" t="s">
+      <c r="G21" s="163"/>
+      <c r="H21" s="95" t="s">
         <v>31</v>
       </c>
-      <c r="I21" s="68"/>
-      <c r="J21" s="69"/>
+      <c r="I21" s="96"/>
+      <c r="J21" s="97"/>
       <c r="K21" s="26"/>
     </row>
-    <row r="22" spans="2:11" ht="15.75" thickBot="1">
-      <c r="F22" s="95"/>
-      <c r="G22" s="96"/>
+    <row r="22" spans="2:11">
+      <c r="F22" s="164"/>
+      <c r="G22" s="164"/>
+    </row>
+    <row r="23" spans="2:11">
+      <c r="F23" s="164"/>
+      <c r="G23" s="164"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="vyuEoK5DDEffeWwxDJKTxx9FX3HNjHl9Y7LdKZgG8ttx81fni5YNsxiQW6hWyzSkAT3Vx1pBl6QBVPR0w8rdsA==" saltValue="+eYfNNLI/Y1Y4nkr6vgXfA==" spinCount="100000" sheet="1" scenarios="1" formatCells="0" formatColumns="0" formatRows="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="YcXydI+PedicbN8GIUKdzyam3R3yyhKY1mugMKtRzcfuvoulPB3eq/2E4JIGLrcI36c5EtkSkEnXMKgmqfL01A==" saltValue="S1WgSHtjbo94CqGsonycNw==" spinCount="100000" sheet="1" scenarios="1" formatCells="0" formatColumns="0" formatRows="0"/>
   <mergeCells count="21">
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="F18:F20"/>
+    <mergeCell ref="J19:J20"/>
+    <mergeCell ref="B18:E20"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="G18:G20"/>
+    <mergeCell ref="F21:G23"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="H16:H17"/>
     <mergeCell ref="F16:F17"/>
@@ -3249,16 +3255,6 @@
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="F7:G7"/>
     <mergeCell ref="F8:G8"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="F18:F20"/>
-    <mergeCell ref="J19:J20"/>
-    <mergeCell ref="B18:E20"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="H19:H20"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="G18:G20"/>
-    <mergeCell ref="F21:G22"/>
   </mergeCells>
   <conditionalFormatting sqref="H19:J19 I20:J20">
     <cfRule type="expression" dxfId="3" priority="4" stopIfTrue="1">
@@ -5353,10 +5349,10 @@
       <c r="I4" s="34"/>
     </row>
     <row r="5" spans="2:9" ht="16.5" thickTop="1">
-      <c r="B5" s="130" t="s">
+      <c r="B5" s="128" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="131"/>
+      <c r="C5" s="129"/>
       <c r="D5" s="34"/>
       <c r="E5" s="34"/>
       <c r="H5" s="34"/>
@@ -5424,36 +5420,36 @@
     </row>
     <row r="11" spans="2:9" ht="16.5" thickTop="1" thickBot="1"/>
     <row r="12" spans="2:9">
-      <c r="B12" s="132" t="s">
+      <c r="B12" s="130" t="s">
         <v>77</v>
       </c>
-      <c r="C12" s="133"/>
-      <c r="D12" s="133"/>
-      <c r="E12" s="133"/>
-      <c r="F12" s="134"/>
+      <c r="C12" s="131"/>
+      <c r="D12" s="131"/>
+      <c r="E12" s="131"/>
+      <c r="F12" s="132"/>
     </row>
     <row r="13" spans="2:9" ht="15.75" thickBot="1">
-      <c r="B13" s="135"/>
-      <c r="C13" s="136"/>
-      <c r="D13" s="136"/>
-      <c r="E13" s="136"/>
-      <c r="F13" s="137"/>
+      <c r="B13" s="133"/>
+      <c r="C13" s="134"/>
+      <c r="D13" s="134"/>
+      <c r="E13" s="134"/>
+      <c r="F13" s="135"/>
     </row>
     <row r="14" spans="2:9" ht="16.899999999999999" customHeight="1">
-      <c r="B14" s="138" t="s">
+      <c r="B14" s="136" t="s">
         <v>78</v>
       </c>
-      <c r="C14" s="139"/>
-      <c r="D14" s="139"/>
-      <c r="E14" s="139"/>
-      <c r="F14" s="140"/>
+      <c r="C14" s="137"/>
+      <c r="D14" s="137"/>
+      <c r="E14" s="137"/>
+      <c r="F14" s="138"/>
     </row>
     <row r="15" spans="2:9" ht="16.899999999999999" customHeight="1" thickBot="1">
-      <c r="B15" s="141"/>
-      <c r="C15" s="142"/>
-      <c r="D15" s="142"/>
-      <c r="E15" s="142"/>
-      <c r="F15" s="143"/>
+      <c r="B15" s="139"/>
+      <c r="C15" s="140"/>
+      <c r="D15" s="140"/>
+      <c r="E15" s="140"/>
+      <c r="F15" s="141"/>
     </row>
     <row r="16" spans="2:9">
       <c r="B16" s="44" t="s">
@@ -5468,16 +5464,16 @@
       <c r="E16" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="F16" s="144" t="s">
+      <c r="F16" s="142" t="s">
         <v>26</v>
       </c>
-      <c r="G16" s="144" t="s">
+      <c r="G16" s="142" t="s">
         <v>27</v>
       </c>
-      <c r="H16" s="153" t="s">
+      <c r="H16" s="150" t="s">
         <v>28</v>
       </c>
-      <c r="I16" s="155"/>
+      <c r="I16" s="152"/>
     </row>
     <row r="17" spans="2:10">
       <c r="B17" s="46">
@@ -5495,20 +5491,20 @@
         <f ca="1">Random!H20</f>
         <v>5</v>
       </c>
-      <c r="F17" s="145"/>
-      <c r="G17" s="145"/>
-      <c r="H17" s="154"/>
-      <c r="I17" s="155"/>
+      <c r="F17" s="143"/>
+      <c r="G17" s="143"/>
+      <c r="H17" s="151"/>
+      <c r="I17" s="152"/>
     </row>
     <row r="18" spans="2:10" ht="14.45" customHeight="1">
-      <c r="B18" s="146" t="s">
+      <c r="B18" s="144" t="s">
         <v>81</v>
       </c>
-      <c r="C18" s="147"/>
-      <c r="D18" s="147"/>
-      <c r="E18" s="148"/>
-      <c r="F18" s="152"/>
-      <c r="G18" s="128" t="s">
+      <c r="C18" s="145"/>
+      <c r="D18" s="145"/>
+      <c r="E18" s="146"/>
+      <c r="F18" s="122"/>
+      <c r="G18" s="121" t="s">
         <v>82</v>
       </c>
       <c r="H18" s="49" t="s">
@@ -5520,12 +5516,12 @@
       <c r="J18" s="51"/>
     </row>
     <row r="19" spans="2:10">
-      <c r="B19" s="146"/>
-      <c r="C19" s="147"/>
-      <c r="D19" s="147"/>
-      <c r="E19" s="148"/>
-      <c r="F19" s="152"/>
-      <c r="G19" s="128"/>
+      <c r="B19" s="144"/>
+      <c r="C19" s="145"/>
+      <c r="D19" s="145"/>
+      <c r="E19" s="146"/>
+      <c r="F19" s="122"/>
+      <c r="G19" s="121"/>
       <c r="H19" s="52" t="e">
         <f>Loans!B17*(1+Loans!C17/Loans!D17)^(Loans!D17*Loans!E17)</f>
         <v>#DIV/0!</v>
@@ -5537,12 +5533,12 @@
       <c r="J19" s="51"/>
     </row>
     <row r="20" spans="2:10" ht="14.45" customHeight="1">
-      <c r="B20" s="146"/>
-      <c r="C20" s="147"/>
-      <c r="D20" s="147"/>
-      <c r="E20" s="148"/>
-      <c r="F20" s="152"/>
-      <c r="G20" s="128" t="s">
+      <c r="B20" s="144"/>
+      <c r="C20" s="145"/>
+      <c r="D20" s="145"/>
+      <c r="E20" s="146"/>
+      <c r="F20" s="122"/>
+      <c r="G20" s="121" t="s">
         <v>85</v>
       </c>
       <c r="H20" s="54" t="s">
@@ -5556,43 +5552,43 @@
       </c>
     </row>
     <row r="21" spans="2:10">
-      <c r="B21" s="146"/>
-      <c r="C21" s="147"/>
-      <c r="D21" s="147"/>
-      <c r="E21" s="148"/>
-      <c r="F21" s="152"/>
-      <c r="G21" s="128"/>
-      <c r="H21" s="156" t="e">
+      <c r="B21" s="144"/>
+      <c r="C21" s="145"/>
+      <c r="D21" s="145"/>
+      <c r="E21" s="146"/>
+      <c r="F21" s="122"/>
+      <c r="G21" s="121"/>
+      <c r="H21" s="153" t="e">
         <f>Loans!B17*((1+Loans!C17/Loans!D17)^(Loans!D17*Loans!E17)-1)/(Loans!C17/Loans!D17)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I21" s="126">
+      <c r="I21" s="125">
         <f>Loans!B17*Loans!D17*Loans!E17</f>
         <v>0</v>
       </c>
-      <c r="J21" s="126" t="e">
+      <c r="J21" s="125" t="e">
         <f>H21-I21</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="22" spans="2:10">
-      <c r="B22" s="146"/>
-      <c r="C22" s="147"/>
-      <c r="D22" s="147"/>
-      <c r="E22" s="148"/>
-      <c r="F22" s="152"/>
-      <c r="G22" s="128"/>
-      <c r="H22" s="156"/>
-      <c r="I22" s="127"/>
-      <c r="J22" s="127"/>
+      <c r="B22" s="144"/>
+      <c r="C22" s="145"/>
+      <c r="D22" s="145"/>
+      <c r="E22" s="146"/>
+      <c r="F22" s="122"/>
+      <c r="G22" s="121"/>
+      <c r="H22" s="153"/>
+      <c r="I22" s="126"/>
+      <c r="J22" s="126"/>
     </row>
     <row r="23" spans="2:10">
-      <c r="B23" s="146"/>
-      <c r="C23" s="147"/>
-      <c r="D23" s="147"/>
-      <c r="E23" s="148"/>
-      <c r="F23" s="152"/>
-      <c r="G23" s="128" t="s">
+      <c r="B23" s="144"/>
+      <c r="C23" s="145"/>
+      <c r="D23" s="145"/>
+      <c r="E23" s="146"/>
+      <c r="F23" s="122"/>
+      <c r="G23" s="121" t="s">
         <v>87</v>
       </c>
       <c r="H23" s="49" t="s">
@@ -5606,35 +5602,35 @@
       </c>
     </row>
     <row r="24" spans="2:10">
-      <c r="B24" s="146"/>
-      <c r="C24" s="147"/>
-      <c r="D24" s="147"/>
-      <c r="E24" s="148"/>
-      <c r="F24" s="152"/>
-      <c r="G24" s="128"/>
-      <c r="H24" s="156" t="e">
+      <c r="B24" s="144"/>
+      <c r="C24" s="145"/>
+      <c r="D24" s="145"/>
+      <c r="E24" s="146"/>
+      <c r="F24" s="122"/>
+      <c r="G24" s="121"/>
+      <c r="H24" s="153" t="e">
         <f>Loans!B17*(Loans!C17/Loans!D17)/(1-(1+Loans!C17/Loans!D17)^(-Loans!D17*Loans!E17))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I24" s="126">
+      <c r="I24" s="125">
         <f>Loans!D17*Loans!E17*Loans!H19</f>
         <v>0</v>
       </c>
-      <c r="J24" s="125">
+      <c r="J24" s="124">
         <f>I24-Loans!B17</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="2:10" ht="17.45" customHeight="1" thickBot="1">
-      <c r="B25" s="149"/>
-      <c r="C25" s="150"/>
-      <c r="D25" s="150"/>
-      <c r="E25" s="151"/>
-      <c r="F25" s="157"/>
-      <c r="G25" s="129"/>
-      <c r="H25" s="156"/>
-      <c r="I25" s="127"/>
-      <c r="J25" s="125"/>
+      <c r="B25" s="147"/>
+      <c r="C25" s="148"/>
+      <c r="D25" s="148"/>
+      <c r="E25" s="149"/>
+      <c r="F25" s="123"/>
+      <c r="G25" s="127"/>
+      <c r="H25" s="153"/>
+      <c r="I25" s="126"/>
+      <c r="J25" s="124"/>
     </row>
     <row r="26" spans="2:10">
       <c r="B26" s="55"/>
@@ -5651,18 +5647,6 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="K6FLfj/2GW8ZCTHv8p2xOh6RoXSFAt/EbNff2TRYiVEiR5k81I441LUk2VqjGrBYfbxIzcyIabf7eIRPuVbGfw==" saltValue="gn8DjQ/CYqWIJUrkECcB7A==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="20">
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="F20:F22"/>
-    <mergeCell ref="G20:G22"/>
-    <mergeCell ref="F23:F25"/>
-    <mergeCell ref="J24:J25"/>
-    <mergeCell ref="J21:J22"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B12:F13"/>
-    <mergeCell ref="B14:F15"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="G16:G17"/>
     <mergeCell ref="B18:E25"/>
     <mergeCell ref="F18:F19"/>
     <mergeCell ref="H16:H17"/>
@@ -5671,6 +5655,18 @@
     <mergeCell ref="I21:I22"/>
     <mergeCell ref="H24:H25"/>
     <mergeCell ref="I24:I25"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B12:F13"/>
+    <mergeCell ref="B14:F15"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="F20:F22"/>
+    <mergeCell ref="G20:G22"/>
+    <mergeCell ref="F23:F25"/>
+    <mergeCell ref="J24:J25"/>
+    <mergeCell ref="J21:J22"/>
+    <mergeCell ref="G23:G25"/>
   </mergeCells>
   <conditionalFormatting sqref="H18:H21">
     <cfRule type="expression" dxfId="1" priority="2">
@@ -5697,34 +5693,34 @@
   <sheetData>
     <row r="1" spans="2:6" ht="15.75" thickBot="1"/>
     <row r="2" spans="2:6">
-      <c r="B2" s="158" t="s">
+      <c r="B2" s="154" t="s">
         <v>91</v>
       </c>
-      <c r="C2" s="159"/>
-      <c r="D2" s="159"/>
-      <c r="E2" s="159"/>
-      <c r="F2" s="160"/>
+      <c r="C2" s="155"/>
+      <c r="D2" s="155"/>
+      <c r="E2" s="155"/>
+      <c r="F2" s="156"/>
     </row>
     <row r="3" spans="2:6">
-      <c r="B3" s="161"/>
-      <c r="C3" s="162"/>
-      <c r="D3" s="162"/>
-      <c r="E3" s="162"/>
-      <c r="F3" s="163"/>
+      <c r="B3" s="157"/>
+      <c r="C3" s="158"/>
+      <c r="D3" s="158"/>
+      <c r="E3" s="158"/>
+      <c r="F3" s="159"/>
     </row>
     <row r="4" spans="2:6">
-      <c r="B4" s="161"/>
-      <c r="C4" s="162"/>
-      <c r="D4" s="162"/>
-      <c r="E4" s="162"/>
-      <c r="F4" s="163"/>
+      <c r="B4" s="157"/>
+      <c r="C4" s="158"/>
+      <c r="D4" s="158"/>
+      <c r="E4" s="158"/>
+      <c r="F4" s="159"/>
     </row>
     <row r="5" spans="2:6" ht="15.75" thickBot="1">
-      <c r="B5" s="164"/>
-      <c r="C5" s="165"/>
-      <c r="D5" s="165"/>
-      <c r="E5" s="165"/>
-      <c r="F5" s="166"/>
+      <c r="B5" s="160"/>
+      <c r="C5" s="161"/>
+      <c r="D5" s="161"/>
+      <c r="E5" s="161"/>
+      <c r="F5" s="162"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5735,6 +5731,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002C289946819CFF499E91D197BC975371" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="674b7a4e239a9748c7aaa97e309327a4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cca9fd2d-ef84-45c9-8063-8f4bd4c29606" xmlns:ns3="18557d39-01b8-4d71-9479-3fad465290ae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="600253478e594d1349e02792803dc53a" ns2:_="" ns3:_="">
     <xsd:import namespace="cca9fd2d-ef84-45c9-8063-8f4bd4c29606"/>
@@ -5951,15 +5956,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -5971,6 +5967,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC22AC1B-1134-480D-984D-E3FB18425132}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8D40D51-EB3D-4F2E-911E-703AF067E6CE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5989,14 +5993,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC22AC1B-1134-480D-984D-E3FB18425132}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBB720F6-9EF9-47F8-8112-CBCB1A8E9176}">
   <ds:schemaRefs>

--- a/144/DQ Templates and Instructions/Topic 4 DQ 2/Topic 4 DQ 2.xlsx
+++ b/144/DQ Templates and Instructions/Topic 4 DQ 2/Topic 4 DQ 2.xlsx
@@ -1,25 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gcumail.sharepoint.com/sites/MathematicsProgramFacultyStaff-MATOFTF/Shared Documents/MATOFTF/ALEKS/DQ Templates and Instructions/Topic 4 DQ 2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="627" documentId="8_{C5F6D942-BE47-4B16-B7DF-0F8A5C8F158C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83675C0D-D250-4902-9B49-D52F8AAAEA40}"/>
+  <xr:revisionPtr revIDLastSave="635" documentId="8_{C5F6D942-BE47-4B16-B7DF-0F8A5C8F158C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{446D4608-C03C-4635-96D0-D96646855B9F}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="21600" windowHeight="11295" xr2:uid="{4FCF7FA6-22BB-4545-AB27-D5B8AACA448D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4FCF7FA6-22BB-4545-AB27-D5B8AACA448D}"/>
   </bookViews>
   <sheets>
     <sheet name="Goals and Instructions" sheetId="5" r:id="rId1"/>
     <sheet name="Loans" sheetId="1" r:id="rId2"/>
-    <sheet name="Random" sheetId="4" state="hidden" r:id="rId3"/>
-    <sheet name="Solutions" sheetId="2" state="hidden" r:id="rId4"/>
-    <sheet name="Sheet2" sheetId="3" state="hidden" r:id="rId5"/>
+    <sheet name="Users" sheetId="6" state="hidden" r:id="rId3"/>
+    <sheet name="Random" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet name="Solutions" sheetId="2" state="hidden" r:id="rId5"/>
+    <sheet name="Sheet2" sheetId="3" state="hidden" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" iterate="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="103">
   <si>
     <t>Excel Skills Learned</t>
   </si>
@@ -364,6 +365,12 @@
   </si>
   <si>
     <t>Your Name Here</t>
+  </si>
+  <si>
+    <t>Names</t>
+  </si>
+  <si>
+    <t>Reset</t>
   </si>
 </sst>
 </file>
@@ -1098,7 +1105,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="165">
+  <cellXfs count="167">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1166,14 +1173,11 @@
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
@@ -1285,11 +1289,11 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="33" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -1320,6 +1324,118 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
@@ -1432,211 +1548,107 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="36" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="30" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="37" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="30" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="37" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1664,13 +1676,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2874,53 +2888,53 @@
       <c r="B2" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="58" t="s">
+      <c r="D2" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="59"/>
-      <c r="I2" s="60"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
+      <c r="I2" s="59"/>
     </row>
     <row r="3" spans="2:9">
       <c r="B3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="61"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="63"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="62"/>
     </row>
     <row r="4" spans="2:9">
       <c r="B4" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="61"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="63"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="61"/>
+      <c r="I4" s="62"/>
     </row>
     <row r="5" spans="2:9">
       <c r="B5" s="12"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="62"/>
-      <c r="F5" s="62"/>
-      <c r="G5" s="62"/>
-      <c r="H5" s="62"/>
-      <c r="I5" s="63"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="62"/>
     </row>
     <row r="6" spans="2:9" ht="15.75" thickBot="1">
-      <c r="D6" s="64"/>
-      <c r="E6" s="65"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="65"/>
-      <c r="I6" s="66"/>
+      <c r="D6" s="63"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="65"/>
     </row>
     <row r="7" spans="2:9" ht="15.75" thickBot="1"/>
     <row r="8" spans="2:9" ht="19.5" thickBot="1">
@@ -2956,9 +2970,9 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3.7109375" style="16" customWidth="1"/>
-    <col min="2" max="2" width="21.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.42578125" style="25" customWidth="1"/>
+    <col min="2" max="2" width="21.28515625" style="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.28515625" style="24" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="10.42578125" style="24" customWidth="1"/>
     <col min="6" max="6" width="25.7109375" style="16" customWidth="1"/>
     <col min="7" max="7" width="30" style="16" customWidth="1"/>
     <col min="8" max="8" width="26.140625" style="17" customWidth="1"/>
@@ -2971,13 +2985,13 @@
       <c r="B2" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="33" t="s">
+      <c r="C2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="D2" s="67" t="s">
+      <c r="D2" s="94" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="68"/>
+      <c r="E2" s="95"/>
       <c r="H2" s="16"/>
       <c r="I2" s="16"/>
     </row>
@@ -2998,20 +3012,20 @@
       <c r="I4" s="16"/>
     </row>
     <row r="5" spans="2:10" ht="16.5" thickTop="1">
-      <c r="B5" s="73" t="s">
+      <c r="B5" s="100" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="74"/>
+      <c r="C5" s="101"/>
       <c r="D5" s="16"/>
       <c r="E5" s="19">
         <v>15</v>
       </c>
-      <c r="F5" s="87" t="s">
+      <c r="F5" s="114" t="s">
         <v>93</v>
       </c>
-      <c r="G5" s="88"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="20"/>
+      <c r="G5" s="115"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
     </row>
     <row r="6" spans="2:10" ht="15.6" customHeight="1">
       <c r="B6" s="1" t="s">
@@ -3021,15 +3035,15 @@
         <v>11</v>
       </c>
       <c r="D6" s="16"/>
-      <c r="E6" s="21">
+      <c r="E6" s="20">
         <v>15</v>
       </c>
-      <c r="F6" s="89" t="s">
+      <c r="F6" s="116" t="s">
         <v>94</v>
       </c>
-      <c r="G6" s="90"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="22"/>
+      <c r="G6" s="117"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="21"/>
     </row>
     <row r="7" spans="2:10" ht="16.149999999999999" customHeight="1">
       <c r="B7" s="3" t="s">
@@ -3039,15 +3053,15 @@
         <v>13</v>
       </c>
       <c r="D7" s="16"/>
-      <c r="E7" s="23">
+      <c r="E7" s="22">
         <v>16</v>
       </c>
-      <c r="F7" s="91" t="s">
+      <c r="F7" s="118" t="s">
         <v>95</v>
       </c>
-      <c r="G7" s="92"/>
-      <c r="H7" s="20"/>
-      <c r="I7" s="20"/>
+      <c r="G7" s="119"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="16"/>
     </row>
     <row r="8" spans="2:10" ht="16.5" thickBot="1">
       <c r="B8" s="5" t="s">
@@ -3057,15 +3071,15 @@
         <v>15</v>
       </c>
       <c r="D8" s="16"/>
-      <c r="E8" s="24">
+      <c r="E8" s="23">
         <v>16</v>
       </c>
-      <c r="F8" s="93" t="s">
+      <c r="F8" s="120" t="s">
         <v>96</v>
       </c>
-      <c r="G8" s="94"/>
-      <c r="H8" s="22"/>
-      <c r="I8" s="22"/>
+      <c r="G8" s="121"/>
+      <c r="H8" s="21"/>
+      <c r="I8" s="21"/>
     </row>
     <row r="9" spans="2:10" ht="15.75">
       <c r="B9" s="6" t="s">
@@ -3076,11 +3090,11 @@
       </c>
       <c r="D9" s="16"/>
       <c r="E9" s="16"/>
-      <c r="F9" s="98" t="s">
+      <c r="F9" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="G9" s="98"/>
-      <c r="H9" s="98"/>
+      <c r="G9" s="69"/>
+      <c r="H9" s="69"/>
       <c r="I9" s="16"/>
     </row>
     <row r="10" spans="2:10" ht="16.5" thickBot="1">
@@ -3097,153 +3111,143 @@
     </row>
     <row r="11" spans="2:10" ht="16.5" thickTop="1" thickBot="1"/>
     <row r="12" spans="2:10" ht="14.45" customHeight="1">
-      <c r="B12" s="75" t="s">
+      <c r="B12" s="102" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="76"/>
-      <c r="D12" s="76"/>
-      <c r="E12" s="76"/>
-      <c r="F12" s="77"/>
+      <c r="C12" s="103"/>
+      <c r="D12" s="103"/>
+      <c r="E12" s="103"/>
+      <c r="F12" s="104"/>
     </row>
     <row r="13" spans="2:10" ht="15.75" thickBot="1">
-      <c r="B13" s="78"/>
-      <c r="C13" s="79"/>
-      <c r="D13" s="79"/>
-      <c r="E13" s="79"/>
-      <c r="F13" s="80"/>
-      <c r="J13" s="26"/>
+      <c r="B13" s="105"/>
+      <c r="C13" s="106"/>
+      <c r="D13" s="106"/>
+      <c r="E13" s="106"/>
+      <c r="F13" s="107"/>
+      <c r="J13" s="25"/>
     </row>
     <row r="14" spans="2:10" ht="16.899999999999999" customHeight="1">
-      <c r="B14" s="81" t="s">
+      <c r="B14" s="108" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="82"/>
-      <c r="D14" s="82"/>
-      <c r="E14" s="82"/>
-      <c r="F14" s="83"/>
+      <c r="C14" s="109"/>
+      <c r="D14" s="109"/>
+      <c r="E14" s="109"/>
+      <c r="F14" s="110"/>
     </row>
     <row r="15" spans="2:10" ht="16.899999999999999" customHeight="1" thickBot="1">
-      <c r="B15" s="84"/>
-      <c r="C15" s="85"/>
-      <c r="D15" s="85"/>
-      <c r="E15" s="85"/>
-      <c r="F15" s="86"/>
+      <c r="B15" s="111"/>
+      <c r="C15" s="112"/>
+      <c r="D15" s="112"/>
+      <c r="E15" s="112"/>
+      <c r="F15" s="113"/>
     </row>
     <row r="16" spans="2:10">
-      <c r="B16" s="27" t="s">
+      <c r="B16" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="C16" s="28" t="s">
+      <c r="C16" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="28" t="s">
+      <c r="D16" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="E16" s="28" t="s">
+      <c r="E16" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="F16" s="71" t="s">
+      <c r="F16" s="98" t="s">
         <v>26</v>
       </c>
-      <c r="G16" s="71" t="s">
+      <c r="G16" s="98" t="s">
         <v>27</v>
       </c>
-      <c r="H16" s="69" t="s">
+      <c r="H16" s="96" t="s">
         <v>28</v>
       </c>
-      <c r="I16" s="113"/>
+      <c r="I16" s="84"/>
     </row>
     <row r="17" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B17" s="56"/>
-      <c r="C17" s="57"/>
-      <c r="D17" s="57"/>
-      <c r="E17" s="57"/>
-      <c r="F17" s="72"/>
-      <c r="G17" s="72"/>
-      <c r="H17" s="70"/>
-      <c r="I17" s="113"/>
+      <c r="B17" s="55"/>
+      <c r="C17" s="56"/>
+      <c r="D17" s="56"/>
+      <c r="E17" s="56"/>
+      <c r="F17" s="99"/>
+      <c r="G17" s="99"/>
+      <c r="H17" s="97"/>
+      <c r="I17" s="84"/>
     </row>
     <row r="18" spans="2:11" ht="14.45" customHeight="1">
-      <c r="B18" s="104" t="str">
+      <c r="B18" s="75" t="str">
         <f ca="1">IF(C2="Your Name Here!", "Enter your name in C2 and your very own problem will appear here:)","Compute the monthly payments to pay back a loan of $"&amp;Random!H19&amp;" in "&amp;Random!H20&amp;" years an APR of "&amp;Random!H21&amp;"% compounded monthly. Find the total amount payed on the loan and the interest payed.")</f>
         <v>Compute the monthly payments to pay back a loan of $2200 in 5 years an APR of 20.29% compounded monthly. Find the total amount payed on the loan and the interest payed.</v>
       </c>
-      <c r="C18" s="105"/>
-      <c r="D18" s="105"/>
-      <c r="E18" s="106"/>
-      <c r="F18" s="99"/>
-      <c r="G18" s="118" t="s">
+      <c r="C18" s="76"/>
+      <c r="D18" s="76"/>
+      <c r="E18" s="77"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="89" t="s">
         <v>97</v>
       </c>
-      <c r="H18" s="29" t="s">
+      <c r="H18" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="I18" s="30" t="s">
+      <c r="I18" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="J18" s="31" t="s">
+      <c r="J18" s="30" t="s">
         <v>99</v>
       </c>
-      <c r="K18" s="26"/>
+      <c r="K18" s="25"/>
     </row>
     <row r="19" spans="2:11">
-      <c r="B19" s="107"/>
-      <c r="C19" s="108"/>
-      <c r="D19" s="108"/>
-      <c r="E19" s="109"/>
-      <c r="F19" s="100"/>
-      <c r="G19" s="119"/>
-      <c r="H19" s="114"/>
-      <c r="I19" s="116"/>
-      <c r="J19" s="102"/>
-      <c r="K19" s="26"/>
+      <c r="B19" s="78"/>
+      <c r="C19" s="79"/>
+      <c r="D19" s="79"/>
+      <c r="E19" s="80"/>
+      <c r="F19" s="71"/>
+      <c r="G19" s="90"/>
+      <c r="H19" s="85"/>
+      <c r="I19" s="87"/>
+      <c r="J19" s="73"/>
+      <c r="K19" s="25"/>
     </row>
     <row r="20" spans="2:11" ht="24" customHeight="1" thickBot="1">
-      <c r="B20" s="110"/>
-      <c r="C20" s="111"/>
-      <c r="D20" s="111"/>
-      <c r="E20" s="112"/>
-      <c r="F20" s="101"/>
-      <c r="G20" s="120"/>
-      <c r="H20" s="115"/>
-      <c r="I20" s="117"/>
-      <c r="J20" s="103"/>
-      <c r="K20" s="26"/>
+      <c r="B20" s="81"/>
+      <c r="C20" s="82"/>
+      <c r="D20" s="82"/>
+      <c r="E20" s="83"/>
+      <c r="F20" s="72"/>
+      <c r="G20" s="91"/>
+      <c r="H20" s="86"/>
+      <c r="I20" s="88"/>
+      <c r="J20" s="74"/>
+      <c r="K20" s="25"/>
     </row>
     <row r="21" spans="2:11" ht="15.75" customHeight="1" thickBot="1">
-      <c r="B21" s="32"/>
-      <c r="F21" s="163" t="s">
+      <c r="B21" s="31"/>
+      <c r="F21" s="92" t="s">
         <v>92</v>
       </c>
-      <c r="G21" s="163"/>
-      <c r="H21" s="95" t="s">
+      <c r="G21" s="92"/>
+      <c r="H21" s="66" t="s">
         <v>31</v>
       </c>
-      <c r="I21" s="96"/>
-      <c r="J21" s="97"/>
-      <c r="K21" s="26"/>
+      <c r="I21" s="67"/>
+      <c r="J21" s="68"/>
+      <c r="K21" s="25"/>
     </row>
     <row r="22" spans="2:11">
-      <c r="F22" s="164"/>
-      <c r="G22" s="164"/>
+      <c r="F22" s="93"/>
+      <c r="G22" s="93"/>
     </row>
     <row r="23" spans="2:11">
-      <c r="F23" s="164"/>
-      <c r="G23" s="164"/>
+      <c r="F23" s="93"/>
+      <c r="G23" s="93"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="YcXydI+PedicbN8GIUKdzyam3R3yyhKY1mugMKtRzcfuvoulPB3eq/2E4JIGLrcI36c5EtkSkEnXMKgmqfL01A==" saltValue="S1WgSHtjbo94CqGsonycNw==" spinCount="100000" sheet="1" scenarios="1" formatCells="0" formatColumns="0" formatRows="0"/>
   <mergeCells count="21">
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="F18:F20"/>
-    <mergeCell ref="J19:J20"/>
-    <mergeCell ref="B18:E20"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="H19:H20"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="G18:G20"/>
-    <mergeCell ref="F21:G23"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="H16:H17"/>
     <mergeCell ref="F16:F17"/>
@@ -3255,6 +3259,16 @@
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="F7:G7"/>
     <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="F18:F20"/>
+    <mergeCell ref="J19:J20"/>
+    <mergeCell ref="B18:E20"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="G18:G20"/>
+    <mergeCell ref="F21:G23"/>
   </mergeCells>
   <conditionalFormatting sqref="H19:J19 I20:J20">
     <cfRule type="expression" dxfId="3" priority="4" stopIfTrue="1">
@@ -3305,6 +3319,172 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDCA09C9-B462-4DFB-8A13-AD4F588A2FD8}">
+  <dimension ref="A1:M21"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="164"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="164" t="s">
+        <v>101</v>
+      </c>
+      <c r="B1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C1" s="165">
+        <v>1</v>
+      </c>
+      <c r="D1" t="str">
+        <f>Loans!C2</f>
+        <v>Your Name Here</v>
+      </c>
+      <c r="F1" s="166" t="str">
+        <f ca="1">IF(M1="ACTIVE", "✓ Tracking Active", "⚠️ ERROR: Enable Iterative Calculations (File &gt; Options &gt; Formulas)")</f>
+        <v>✓ Tracking Active</v>
+      </c>
+      <c r="G1" s="166"/>
+      <c r="H1" s="166"/>
+      <c r="I1" s="166"/>
+      <c r="J1" s="166"/>
+      <c r="K1" s="166"/>
+      <c r="L1" s="166"/>
+      <c r="M1" s="164" t="str">
+        <f ca="1">IF(M1="ACTIVE", "ACTIVE", "ACTIVE")</f>
+        <v>ACTIVE</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="164" t="str">
+        <f t="shared" ref="A2:A19" ca="1" si="0">IF(D$1&lt;&gt;A3,A3,A2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="164" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="164" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="164" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="164" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="164" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="164" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="164" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="164" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="164" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="164" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="164" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="164" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" s="164" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" s="164" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="164" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="164" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="164" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="164" t="str">
+        <f ca="1">IF(D$1&lt;&gt;A21,A21,A20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="164" t="str">
+        <f ca="1">IF(C1="","",IF(D$1&lt;&gt;A21,D$1,A21))</f>
+        <v>Your Name Here</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="w3b5SYzXNYOLUVZP5zZQ3LemDVBoFHSpMMGiepwWNJLEtG4eiH/0sxuU2YrplXV3Z+GKUy490EF/7hyo1Xlb8g==" saltValue="77G5M+HyCBp/nt5ek/Kc0w==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <mergeCells count="1">
+    <mergeCell ref="F1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D87AA56-18AC-4DC7-BC45-323D5E38D83F}">
   <dimension ref="A1:W55"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -5305,348 +5485,356 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE723ACA-9738-4B60-95AB-B3B2AD139FFF}">
   <dimension ref="B2:J27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.7109375" style="34" customWidth="1"/>
-    <col min="2" max="2" width="21.28515625" style="43" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.28515625" style="43" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.42578125" style="43" customWidth="1"/>
-    <col min="6" max="6" width="17.42578125" style="34" customWidth="1"/>
-    <col min="7" max="7" width="23.28515625" style="34" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="26.140625" style="37" customWidth="1"/>
-    <col min="9" max="9" width="22.28515625" style="38" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.28515625" style="34" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="34"/>
+    <col min="1" max="1" width="3.7109375" style="33" customWidth="1"/>
+    <col min="2" max="2" width="21.28515625" style="42" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.28515625" style="42" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="10.42578125" style="42" customWidth="1"/>
+    <col min="6" max="6" width="17.42578125" style="33" customWidth="1"/>
+    <col min="7" max="7" width="23.28515625" style="33" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.140625" style="36" customWidth="1"/>
+    <col min="9" max="9" width="22.28515625" style="37" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.28515625" style="33" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="33"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:9">
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
     </row>
     <row r="3" spans="2:9">
-      <c r="B3" s="37"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="33"/>
     </row>
     <row r="4" spans="2:9" ht="15.75" thickBot="1">
-      <c r="B4" s="37"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="H4" s="34"/>
-      <c r="I4" s="34"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="H4" s="33"/>
+      <c r="I4" s="33"/>
     </row>
     <row r="5" spans="2:9" ht="16.5" thickTop="1">
-      <c r="B5" s="128" t="s">
+      <c r="B5" s="135" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="129"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="H5" s="34"/>
-      <c r="I5" s="34"/>
+      <c r="C5" s="136"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="H5" s="33"/>
+      <c r="I5" s="33"/>
     </row>
     <row r="6" spans="2:9" ht="15.75">
-      <c r="B6" s="39" t="s">
+      <c r="B6" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="40" t="s">
+      <c r="C6" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34"/>
-      <c r="H6" s="34"/>
-      <c r="I6" s="34"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="33"/>
     </row>
     <row r="7" spans="2:9" ht="15.75">
-      <c r="B7" s="39" t="s">
+      <c r="B7" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="40" t="s">
+      <c r="C7" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-      <c r="H7" s="34"/>
-      <c r="I7" s="34"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="33"/>
+      <c r="H7" s="33"/>
+      <c r="I7" s="33"/>
     </row>
     <row r="8" spans="2:9" ht="15.75">
-      <c r="B8" s="39" t="s">
+      <c r="B8" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="40" t="s">
+      <c r="C8" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="34"/>
-      <c r="E8" s="34"/>
-      <c r="H8" s="34"/>
-      <c r="I8" s="34"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="33"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="33"/>
     </row>
     <row r="9" spans="2:9" ht="15.75">
-      <c r="B9" s="39" t="s">
+      <c r="B9" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="40" t="s">
+      <c r="C9" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
-      <c r="H9" s="34"/>
-      <c r="I9" s="34"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="33"/>
+      <c r="H9" s="33"/>
+      <c r="I9" s="33"/>
     </row>
     <row r="10" spans="2:9" ht="16.5" thickBot="1">
-      <c r="B10" s="41" t="s">
+      <c r="B10" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="42" t="s">
+      <c r="C10" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="34"/>
-      <c r="E10" s="34"/>
-      <c r="H10" s="34"/>
-      <c r="I10" s="34"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="33"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="33"/>
     </row>
     <row r="11" spans="2:9" ht="16.5" thickTop="1" thickBot="1"/>
     <row r="12" spans="2:9">
-      <c r="B12" s="130" t="s">
+      <c r="B12" s="137" t="s">
         <v>77</v>
       </c>
-      <c r="C12" s="131"/>
-      <c r="D12" s="131"/>
-      <c r="E12" s="131"/>
-      <c r="F12" s="132"/>
+      <c r="C12" s="138"/>
+      <c r="D12" s="138"/>
+      <c r="E12" s="138"/>
+      <c r="F12" s="139"/>
     </row>
     <row r="13" spans="2:9" ht="15.75" thickBot="1">
-      <c r="B13" s="133"/>
-      <c r="C13" s="134"/>
-      <c r="D13" s="134"/>
-      <c r="E13" s="134"/>
-      <c r="F13" s="135"/>
+      <c r="B13" s="140"/>
+      <c r="C13" s="141"/>
+      <c r="D13" s="141"/>
+      <c r="E13" s="141"/>
+      <c r="F13" s="142"/>
     </row>
     <row r="14" spans="2:9" ht="16.899999999999999" customHeight="1">
-      <c r="B14" s="136" t="s">
+      <c r="B14" s="143" t="s">
         <v>78</v>
       </c>
-      <c r="C14" s="137"/>
-      <c r="D14" s="137"/>
-      <c r="E14" s="137"/>
-      <c r="F14" s="138"/>
+      <c r="C14" s="144"/>
+      <c r="D14" s="144"/>
+      <c r="E14" s="144"/>
+      <c r="F14" s="145"/>
     </row>
     <row r="15" spans="2:9" ht="16.899999999999999" customHeight="1" thickBot="1">
-      <c r="B15" s="139"/>
-      <c r="C15" s="140"/>
-      <c r="D15" s="140"/>
-      <c r="E15" s="140"/>
-      <c r="F15" s="141"/>
+      <c r="B15" s="146"/>
+      <c r="C15" s="147"/>
+      <c r="D15" s="147"/>
+      <c r="E15" s="147"/>
+      <c r="F15" s="148"/>
     </row>
     <row r="16" spans="2:9">
-      <c r="B16" s="44" t="s">
+      <c r="B16" s="43" t="s">
         <v>79</v>
       </c>
-      <c r="C16" s="45" t="s">
+      <c r="C16" s="44" t="s">
         <v>80</v>
       </c>
-      <c r="D16" s="45" t="s">
+      <c r="D16" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="E16" s="45" t="s">
+      <c r="E16" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="F16" s="142" t="s">
+      <c r="F16" s="149" t="s">
         <v>26</v>
       </c>
-      <c r="G16" s="142" t="s">
+      <c r="G16" s="149" t="s">
         <v>27</v>
       </c>
-      <c r="H16" s="150" t="s">
+      <c r="H16" s="129" t="s">
         <v>28</v>
       </c>
-      <c r="I16" s="152"/>
+      <c r="I16" s="131"/>
     </row>
     <row r="17" spans="2:10">
-      <c r="B17" s="46">
+      <c r="B17" s="45">
         <f ca="1">Random!H19</f>
         <v>2200</v>
       </c>
-      <c r="C17" s="47">
+      <c r="C17" s="46">
         <f ca="1">Random!H21%</f>
         <v>0.2029</v>
       </c>
-      <c r="D17" s="48">
+      <c r="D17" s="47">
         <v>12</v>
       </c>
-      <c r="E17" s="48">
+      <c r="E17" s="47">
         <f ca="1">Random!H20</f>
         <v>5</v>
       </c>
-      <c r="F17" s="143"/>
-      <c r="G17" s="143"/>
-      <c r="H17" s="151"/>
-      <c r="I17" s="152"/>
+      <c r="F17" s="150"/>
+      <c r="G17" s="150"/>
+      <c r="H17" s="130"/>
+      <c r="I17" s="131"/>
     </row>
     <row r="18" spans="2:10" ht="14.45" customHeight="1">
-      <c r="B18" s="144" t="s">
+      <c r="B18" s="122" t="s">
         <v>81</v>
       </c>
-      <c r="C18" s="145"/>
-      <c r="D18" s="145"/>
-      <c r="E18" s="146"/>
-      <c r="F18" s="122"/>
-      <c r="G18" s="121" t="s">
+      <c r="C18" s="123"/>
+      <c r="D18" s="123"/>
+      <c r="E18" s="124"/>
+      <c r="F18" s="128"/>
+      <c r="G18" s="151" t="s">
         <v>82</v>
       </c>
-      <c r="H18" s="49" t="s">
+      <c r="H18" s="48" t="s">
         <v>83</v>
       </c>
-      <c r="I18" s="50" t="s">
+      <c r="I18" s="49" t="s">
         <v>84</v>
       </c>
-      <c r="J18" s="51"/>
+      <c r="J18" s="50"/>
     </row>
     <row r="19" spans="2:10">
-      <c r="B19" s="144"/>
-      <c r="C19" s="145"/>
-      <c r="D19" s="145"/>
-      <c r="E19" s="146"/>
-      <c r="F19" s="122"/>
-      <c r="G19" s="121"/>
-      <c r="H19" s="52" t="e">
+      <c r="B19" s="122"/>
+      <c r="C19" s="123"/>
+      <c r="D19" s="123"/>
+      <c r="E19" s="124"/>
+      <c r="F19" s="128"/>
+      <c r="G19" s="151"/>
+      <c r="H19" s="51" t="e">
         <f>Loans!B17*(1+Loans!C17/Loans!D17)^(Loans!D17*Loans!E17)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I19" s="53" t="e">
+      <c r="I19" s="52" t="e">
         <f>H19-Loans!B17</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J19" s="51"/>
+      <c r="J19" s="50"/>
     </row>
     <row r="20" spans="2:10" ht="14.45" customHeight="1">
-      <c r="B20" s="144"/>
-      <c r="C20" s="145"/>
-      <c r="D20" s="145"/>
-      <c r="E20" s="146"/>
-      <c r="F20" s="122"/>
-      <c r="G20" s="121" t="s">
+      <c r="B20" s="122"/>
+      <c r="C20" s="123"/>
+      <c r="D20" s="123"/>
+      <c r="E20" s="124"/>
+      <c r="F20" s="128"/>
+      <c r="G20" s="151" t="s">
         <v>85</v>
       </c>
-      <c r="H20" s="54" t="s">
+      <c r="H20" s="53" t="s">
         <v>83</v>
       </c>
-      <c r="I20" s="50" t="s">
+      <c r="I20" s="49" t="s">
         <v>86</v>
       </c>
-      <c r="J20" s="50" t="s">
+      <c r="J20" s="49" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="21" spans="2:10">
-      <c r="B21" s="144"/>
-      <c r="C21" s="145"/>
-      <c r="D21" s="145"/>
-      <c r="E21" s="146"/>
-      <c r="F21" s="122"/>
-      <c r="G21" s="121"/>
-      <c r="H21" s="153" t="e">
+      <c r="B21" s="122"/>
+      <c r="C21" s="123"/>
+      <c r="D21" s="123"/>
+      <c r="E21" s="124"/>
+      <c r="F21" s="128"/>
+      <c r="G21" s="151"/>
+      <c r="H21" s="132" t="e">
         <f>Loans!B17*((1+Loans!C17/Loans!D17)^(Loans!D17*Loans!E17)-1)/(Loans!C17/Loans!D17)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I21" s="125">
+      <c r="I21" s="133">
         <f>Loans!B17*Loans!D17*Loans!E17</f>
         <v>0</v>
       </c>
-      <c r="J21" s="125" t="e">
+      <c r="J21" s="133" t="e">
         <f>H21-I21</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="22" spans="2:10">
-      <c r="B22" s="144"/>
-      <c r="C22" s="145"/>
-      <c r="D22" s="145"/>
-      <c r="E22" s="146"/>
-      <c r="F22" s="122"/>
-      <c r="G22" s="121"/>
-      <c r="H22" s="153"/>
-      <c r="I22" s="126"/>
-      <c r="J22" s="126"/>
+      <c r="B22" s="122"/>
+      <c r="C22" s="123"/>
+      <c r="D22" s="123"/>
+      <c r="E22" s="124"/>
+      <c r="F22" s="128"/>
+      <c r="G22" s="151"/>
+      <c r="H22" s="132"/>
+      <c r="I22" s="134"/>
+      <c r="J22" s="134"/>
     </row>
     <row r="23" spans="2:10">
-      <c r="B23" s="144"/>
-      <c r="C23" s="145"/>
-      <c r="D23" s="145"/>
-      <c r="E23" s="146"/>
-      <c r="F23" s="122"/>
-      <c r="G23" s="121" t="s">
+      <c r="B23" s="122"/>
+      <c r="C23" s="123"/>
+      <c r="D23" s="123"/>
+      <c r="E23" s="124"/>
+      <c r="F23" s="128"/>
+      <c r="G23" s="151" t="s">
         <v>87</v>
       </c>
-      <c r="H23" s="49" t="s">
+      <c r="H23" s="48" t="s">
         <v>88</v>
       </c>
-      <c r="I23" s="50" t="s">
+      <c r="I23" s="49" t="s">
         <v>89</v>
       </c>
-      <c r="J23" s="50" t="s">
+      <c r="J23" s="49" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="24" spans="2:10">
-      <c r="B24" s="144"/>
-      <c r="C24" s="145"/>
-      <c r="D24" s="145"/>
-      <c r="E24" s="146"/>
-      <c r="F24" s="122"/>
-      <c r="G24" s="121"/>
-      <c r="H24" s="153" t="e">
+      <c r="B24" s="122"/>
+      <c r="C24" s="123"/>
+      <c r="D24" s="123"/>
+      <c r="E24" s="124"/>
+      <c r="F24" s="128"/>
+      <c r="G24" s="151"/>
+      <c r="H24" s="132" t="e">
         <f>Loans!B17*(Loans!C17/Loans!D17)/(1-(1+Loans!C17/Loans!D17)^(-Loans!D17*Loans!E17))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I24" s="125">
+      <c r="I24" s="133">
         <f>Loans!D17*Loans!E17*Loans!H19</f>
         <v>0</v>
       </c>
-      <c r="J24" s="124">
+      <c r="J24" s="153">
         <f>I24-Loans!B17</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="2:10" ht="17.45" customHeight="1" thickBot="1">
-      <c r="B25" s="147"/>
-      <c r="C25" s="148"/>
-      <c r="D25" s="148"/>
-      <c r="E25" s="149"/>
-      <c r="F25" s="123"/>
-      <c r="G25" s="127"/>
-      <c r="H25" s="153"/>
-      <c r="I25" s="126"/>
-      <c r="J25" s="124"/>
+      <c r="B25" s="125"/>
+      <c r="C25" s="126"/>
+      <c r="D25" s="126"/>
+      <c r="E25" s="127"/>
+      <c r="F25" s="152"/>
+      <c r="G25" s="154"/>
+      <c r="H25" s="132"/>
+      <c r="I25" s="134"/>
+      <c r="J25" s="153"/>
     </row>
     <row r="26" spans="2:10">
-      <c r="B26" s="55"/>
-      <c r="I26" s="34"/>
+      <c r="B26" s="54"/>
+      <c r="I26" s="33"/>
     </row>
     <row r="27" spans="2:10">
-      <c r="B27" s="38"/>
-      <c r="C27" s="34"/>
-      <c r="D27" s="34"/>
-      <c r="E27" s="34"/>
-      <c r="H27" s="34"/>
-      <c r="I27" s="34"/>
+      <c r="B27" s="37"/>
+      <c r="C27" s="33"/>
+      <c r="D27" s="33"/>
+      <c r="E27" s="33"/>
+      <c r="H27" s="33"/>
+      <c r="I27" s="33"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="K6FLfj/2GW8ZCTHv8p2xOh6RoXSFAt/EbNff2TRYiVEiR5k81I441LUk2VqjGrBYfbxIzcyIabf7eIRPuVbGfw==" saltValue="gn8DjQ/CYqWIJUrkECcB7A==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="20">
+    <mergeCell ref="J24:J25"/>
+    <mergeCell ref="J21:J22"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B12:F13"/>
+    <mergeCell ref="B14:F15"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="G16:G17"/>
     <mergeCell ref="B18:E25"/>
     <mergeCell ref="F18:F19"/>
     <mergeCell ref="H16:H17"/>
@@ -5655,18 +5843,10 @@
     <mergeCell ref="I21:I22"/>
     <mergeCell ref="H24:H25"/>
     <mergeCell ref="I24:I25"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B12:F13"/>
-    <mergeCell ref="B14:F15"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="G16:G17"/>
     <mergeCell ref="G18:G19"/>
     <mergeCell ref="F20:F22"/>
     <mergeCell ref="G20:G22"/>
     <mergeCell ref="F23:F25"/>
-    <mergeCell ref="J24:J25"/>
-    <mergeCell ref="J21:J22"/>
-    <mergeCell ref="G23:G25"/>
   </mergeCells>
   <conditionalFormatting sqref="H18:H21">
     <cfRule type="expression" dxfId="1" priority="2">
@@ -5683,7 +5863,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{262A2B2D-0544-4AF4-8F48-1115B33F73A4}">
   <dimension ref="B1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -5693,34 +5873,34 @@
   <sheetData>
     <row r="1" spans="2:6" ht="15.75" thickBot="1"/>
     <row r="2" spans="2:6">
-      <c r="B2" s="154" t="s">
+      <c r="B2" s="155" t="s">
         <v>91</v>
       </c>
-      <c r="C2" s="155"/>
-      <c r="D2" s="155"/>
-      <c r="E2" s="155"/>
-      <c r="F2" s="156"/>
+      <c r="C2" s="156"/>
+      <c r="D2" s="156"/>
+      <c r="E2" s="156"/>
+      <c r="F2" s="157"/>
     </row>
     <row r="3" spans="2:6">
-      <c r="B3" s="157"/>
-      <c r="C3" s="158"/>
-      <c r="D3" s="158"/>
-      <c r="E3" s="158"/>
-      <c r="F3" s="159"/>
+      <c r="B3" s="158"/>
+      <c r="C3" s="159"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="160"/>
     </row>
     <row r="4" spans="2:6">
-      <c r="B4" s="157"/>
-      <c r="C4" s="158"/>
-      <c r="D4" s="158"/>
-      <c r="E4" s="158"/>
-      <c r="F4" s="159"/>
+      <c r="B4" s="158"/>
+      <c r="C4" s="159"/>
+      <c r="D4" s="159"/>
+      <c r="E4" s="159"/>
+      <c r="F4" s="160"/>
     </row>
     <row r="5" spans="2:6" ht="15.75" thickBot="1">
-      <c r="B5" s="160"/>
-      <c r="C5" s="161"/>
-      <c r="D5" s="161"/>
-      <c r="E5" s="161"/>
-      <c r="F5" s="162"/>
+      <c r="B5" s="161"/>
+      <c r="C5" s="162"/>
+      <c r="D5" s="162"/>
+      <c r="E5" s="162"/>
+      <c r="F5" s="163"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5731,12 +5911,13 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cca9fd2d-ef84-45c9-8063-8f4bd4c29606">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5957,19 +6138,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cca9fd2d-ef84-45c9-8063-8f4bd4c29606">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC22AC1B-1134-480D-984D-E3FB18425132}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBB720F6-9EF9-47F8-8112-CBCB1A8E9176}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="cca9fd2d-ef84-45c9-8063-8f4bd4c29606"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -5994,11 +6176,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBB720F6-9EF9-47F8-8112-CBCB1A8E9176}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC22AC1B-1134-480D-984D-E3FB18425132}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="cca9fd2d-ef84-45c9-8063-8f4bd4c29606"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/144/DQ Templates and Instructions/Topic 4 DQ 2/Topic 4 DQ 2.xlsx
+++ b/144/DQ Templates and Instructions/Topic 4 DQ 2/Topic 4 DQ 2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gcumail.sharepoint.com/sites/MathematicsProgramFacultyStaff-MATOFTF/Shared Documents/MATOFTF/ALEKS/DQ Templates and Instructions/Topic 4 DQ 2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="635" documentId="8_{C5F6D942-BE47-4B16-B7DF-0F8A5C8F158C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{446D4608-C03C-4635-96D0-D96646855B9F}"/>
+  <xr:revisionPtr revIDLastSave="639" documentId="8_{C5F6D942-BE47-4B16-B7DF-0F8A5C8F158C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC73BF01-DF33-4965-8D6B-73DA44682DE0}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4FCF7FA6-22BB-4545-AB27-D5B8AACA448D}"/>
   </bookViews>
@@ -1297,6 +1297,13 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -1548,6 +1555,80 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1566,9 +1647,6 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1581,74 +1659,6 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1675,16 +1685,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1856,10 +1856,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:r>
                       <a:rPr lang="en-US" sz="1100" b="0" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -2064,10 +2061,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:r>
                       <a:rPr lang="en-US" sz="1100" b="0" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -2316,10 +2310,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:r>
                       <a:rPr lang="en-US" sz="1100" b="0" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -2888,53 +2879,53 @@
       <c r="B2" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="57" t="s">
+      <c r="D2" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="59"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="61"/>
     </row>
     <row r="3" spans="2:9">
       <c r="B3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="60"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="61"/>
-      <c r="H3" s="61"/>
-      <c r="I3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="64"/>
     </row>
     <row r="4" spans="2:9">
       <c r="B4" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="60"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="61"/>
-      <c r="G4" s="61"/>
-      <c r="H4" s="61"/>
-      <c r="I4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="63"/>
+      <c r="F4" s="63"/>
+      <c r="G4" s="63"/>
+      <c r="H4" s="63"/>
+      <c r="I4" s="64"/>
     </row>
     <row r="5" spans="2:9">
       <c r="B5" s="12"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="63"/>
+      <c r="F5" s="63"/>
+      <c r="G5" s="63"/>
+      <c r="H5" s="63"/>
+      <c r="I5" s="64"/>
     </row>
     <row r="6" spans="2:9" ht="15.75" thickBot="1">
-      <c r="D6" s="63"/>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="65"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="66"/>
+      <c r="I6" s="67"/>
     </row>
     <row r="7" spans="2:9" ht="15.75" thickBot="1"/>
     <row r="8" spans="2:9" ht="19.5" thickBot="1">
@@ -2988,10 +2979,10 @@
       <c r="C2" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="D2" s="94" t="s">
+      <c r="D2" s="96" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="95"/>
+      <c r="E2" s="97"/>
       <c r="H2" s="16"/>
       <c r="I2" s="16"/>
     </row>
@@ -3012,18 +3003,18 @@
       <c r="I4" s="16"/>
     </row>
     <row r="5" spans="2:10" ht="16.5" thickTop="1">
-      <c r="B5" s="100" t="s">
+      <c r="B5" s="102" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="101"/>
+      <c r="C5" s="103"/>
       <c r="D5" s="16"/>
       <c r="E5" s="19">
         <v>15</v>
       </c>
-      <c r="F5" s="114" t="s">
+      <c r="F5" s="116" t="s">
         <v>93</v>
       </c>
-      <c r="G5" s="115"/>
+      <c r="G5" s="117"/>
       <c r="H5" s="16"/>
       <c r="I5" s="16"/>
     </row>
@@ -3038,10 +3029,10 @@
       <c r="E6" s="20">
         <v>15</v>
       </c>
-      <c r="F6" s="116" t="s">
+      <c r="F6" s="118" t="s">
         <v>94</v>
       </c>
-      <c r="G6" s="117"/>
+      <c r="G6" s="119"/>
       <c r="H6" s="21"/>
       <c r="I6" s="21"/>
     </row>
@@ -3056,10 +3047,10 @@
       <c r="E7" s="22">
         <v>16</v>
       </c>
-      <c r="F7" s="118" t="s">
+      <c r="F7" s="120" t="s">
         <v>95</v>
       </c>
-      <c r="G7" s="119"/>
+      <c r="G7" s="121"/>
       <c r="H7" s="16"/>
       <c r="I7" s="16"/>
     </row>
@@ -3074,10 +3065,10 @@
       <c r="E8" s="23">
         <v>16</v>
       </c>
-      <c r="F8" s="120" t="s">
+      <c r="F8" s="122" t="s">
         <v>96</v>
       </c>
-      <c r="G8" s="121"/>
+      <c r="G8" s="123"/>
       <c r="H8" s="21"/>
       <c r="I8" s="21"/>
     </row>
@@ -3090,11 +3081,11 @@
       </c>
       <c r="D9" s="16"/>
       <c r="E9" s="16"/>
-      <c r="F9" s="69" t="s">
+      <c r="F9" s="71" t="s">
         <v>18</v>
       </c>
-      <c r="G9" s="69"/>
-      <c r="H9" s="69"/>
+      <c r="G9" s="71"/>
+      <c r="H9" s="71"/>
       <c r="I9" s="16"/>
     </row>
     <row r="10" spans="2:10" ht="16.5" thickBot="1">
@@ -3111,37 +3102,37 @@
     </row>
     <row r="11" spans="2:10" ht="16.5" thickTop="1" thickBot="1"/>
     <row r="12" spans="2:10" ht="14.45" customHeight="1">
-      <c r="B12" s="102" t="s">
+      <c r="B12" s="104" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="103"/>
-      <c r="D12" s="103"/>
-      <c r="E12" s="103"/>
-      <c r="F12" s="104"/>
+      <c r="C12" s="105"/>
+      <c r="D12" s="105"/>
+      <c r="E12" s="105"/>
+      <c r="F12" s="106"/>
     </row>
     <row r="13" spans="2:10" ht="15.75" thickBot="1">
-      <c r="B13" s="105"/>
-      <c r="C13" s="106"/>
-      <c r="D13" s="106"/>
-      <c r="E13" s="106"/>
-      <c r="F13" s="107"/>
+      <c r="B13" s="107"/>
+      <c r="C13" s="108"/>
+      <c r="D13" s="108"/>
+      <c r="E13" s="108"/>
+      <c r="F13" s="109"/>
       <c r="J13" s="25"/>
     </row>
     <row r="14" spans="2:10" ht="16.899999999999999" customHeight="1">
-      <c r="B14" s="108" t="s">
+      <c r="B14" s="110" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="109"/>
-      <c r="D14" s="109"/>
-      <c r="E14" s="109"/>
-      <c r="F14" s="110"/>
+      <c r="C14" s="111"/>
+      <c r="D14" s="111"/>
+      <c r="E14" s="111"/>
+      <c r="F14" s="112"/>
     </row>
     <row r="15" spans="2:10" ht="16.899999999999999" customHeight="1" thickBot="1">
-      <c r="B15" s="111"/>
-      <c r="C15" s="112"/>
-      <c r="D15" s="112"/>
-      <c r="E15" s="112"/>
-      <c r="F15" s="113"/>
+      <c r="B15" s="113"/>
+      <c r="C15" s="114"/>
+      <c r="D15" s="114"/>
+      <c r="E15" s="114"/>
+      <c r="F15" s="115"/>
     </row>
     <row r="16" spans="2:10">
       <c r="B16" s="26" t="s">
@@ -3156,37 +3147,37 @@
       <c r="E16" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="F16" s="98" t="s">
+      <c r="F16" s="100" t="s">
         <v>26</v>
       </c>
-      <c r="G16" s="98" t="s">
+      <c r="G16" s="100" t="s">
         <v>27</v>
       </c>
-      <c r="H16" s="96" t="s">
+      <c r="H16" s="98" t="s">
         <v>28</v>
       </c>
-      <c r="I16" s="84"/>
+      <c r="I16" s="86"/>
     </row>
     <row r="17" spans="2:11" ht="15.75" thickBot="1">
       <c r="B17" s="55"/>
       <c r="C17" s="56"/>
       <c r="D17" s="56"/>
       <c r="E17" s="56"/>
-      <c r="F17" s="99"/>
-      <c r="G17" s="99"/>
-      <c r="H17" s="97"/>
-      <c r="I17" s="84"/>
+      <c r="F17" s="101"/>
+      <c r="G17" s="101"/>
+      <c r="H17" s="99"/>
+      <c r="I17" s="86"/>
     </row>
     <row r="18" spans="2:11" ht="14.45" customHeight="1">
-      <c r="B18" s="75" t="str">
-        <f ca="1">IF(C2="Your Name Here!", "Enter your name in C2 and your very own problem will appear here:)","Compute the monthly payments to pay back a loan of $"&amp;Random!H19&amp;" in "&amp;Random!H20&amp;" years an APR of "&amp;Random!H21&amp;"% compounded monthly. Find the total amount payed on the loan and the interest payed.")</f>
-        <v>Compute the monthly payments to pay back a loan of $2200 in 5 years an APR of 20.29% compounded monthly. Find the total amount payed on the loan and the interest payed.</v>
-      </c>
-      <c r="C18" s="76"/>
-      <c r="D18" s="76"/>
-      <c r="E18" s="77"/>
-      <c r="F18" s="70"/>
-      <c r="G18" s="89" t="s">
+      <c r="B18" s="77" t="str">
+        <f ca="1">IF(C2="Your Name Here!", "Enter your name in C2 and your very own problem will appear here:)","Compute the monthly payments to pay back a loan of $"&amp;Random!H19&amp;" in "&amp;Random!H20&amp;" years an APR of "&amp;Random!H21&amp;"% compounded monthly. Find the total amount paid on the loan and the interest paid.")</f>
+        <v>Compute the monthly payments to pay back a loan of $2200 in 5 years an APR of 20.29% compounded monthly. Find the total amount paid on the loan and the interest paid.</v>
+      </c>
+      <c r="C18" s="78"/>
+      <c r="D18" s="78"/>
+      <c r="E18" s="79"/>
+      <c r="F18" s="72"/>
+      <c r="G18" s="91" t="s">
         <v>97</v>
       </c>
       <c r="H18" s="28" t="s">
@@ -3201,52 +3192,52 @@
       <c r="K18" s="25"/>
     </row>
     <row r="19" spans="2:11">
-      <c r="B19" s="78"/>
-      <c r="C19" s="79"/>
-      <c r="D19" s="79"/>
-      <c r="E19" s="80"/>
-      <c r="F19" s="71"/>
-      <c r="G19" s="90"/>
-      <c r="H19" s="85"/>
-      <c r="I19" s="87"/>
-      <c r="J19" s="73"/>
+      <c r="B19" s="80"/>
+      <c r="C19" s="81"/>
+      <c r="D19" s="81"/>
+      <c r="E19" s="82"/>
+      <c r="F19" s="73"/>
+      <c r="G19" s="92"/>
+      <c r="H19" s="87"/>
+      <c r="I19" s="89"/>
+      <c r="J19" s="75"/>
       <c r="K19" s="25"/>
     </row>
     <row r="20" spans="2:11" ht="24" customHeight="1" thickBot="1">
-      <c r="B20" s="81"/>
-      <c r="C20" s="82"/>
-      <c r="D20" s="82"/>
-      <c r="E20" s="83"/>
-      <c r="F20" s="72"/>
-      <c r="G20" s="91"/>
-      <c r="H20" s="86"/>
-      <c r="I20" s="88"/>
-      <c r="J20" s="74"/>
+      <c r="B20" s="83"/>
+      <c r="C20" s="84"/>
+      <c r="D20" s="84"/>
+      <c r="E20" s="85"/>
+      <c r="F20" s="74"/>
+      <c r="G20" s="93"/>
+      <c r="H20" s="88"/>
+      <c r="I20" s="90"/>
+      <c r="J20" s="76"/>
       <c r="K20" s="25"/>
     </row>
     <row r="21" spans="2:11" ht="15.75" customHeight="1" thickBot="1">
       <c r="B21" s="31"/>
-      <c r="F21" s="92" t="s">
+      <c r="F21" s="94" t="s">
         <v>92</v>
       </c>
-      <c r="G21" s="92"/>
-      <c r="H21" s="66" t="s">
+      <c r="G21" s="94"/>
+      <c r="H21" s="68" t="s">
         <v>31</v>
       </c>
-      <c r="I21" s="67"/>
-      <c r="J21" s="68"/>
+      <c r="I21" s="69"/>
+      <c r="J21" s="70"/>
       <c r="K21" s="25"/>
     </row>
     <row r="22" spans="2:11">
-      <c r="F22" s="93"/>
-      <c r="G22" s="93"/>
+      <c r="F22" s="95"/>
+      <c r="G22" s="95"/>
     </row>
     <row r="23" spans="2:11">
-      <c r="F23" s="93"/>
-      <c r="G23" s="93"/>
+      <c r="F23" s="95"/>
+      <c r="G23" s="95"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="YcXydI+PedicbN8GIUKdzyam3R3yyhKY1mugMKtRzcfuvoulPB3eq/2E4JIGLrcI36c5EtkSkEnXMKgmqfL01A==" saltValue="S1WgSHtjbo94CqGsonycNw==" spinCount="100000" sheet="1" scenarios="1" formatCells="0" formatColumns="0" formatRows="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="WdYexBP8o/GsZb4eqqqIdq007Vi0aifo9PneKCwYxilSdq9wv74godOHPyxbn5KCv8VDXhD+NUDMfDopBNumwQ==" saltValue="lnPy0dVlM+28AdP0o7+l0A==" spinCount="100000" sheet="1" scenarios="1" formatCells="0" formatColumns="0" formatRows="0"/>
   <mergeCells count="21">
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="H16:H17"/>
@@ -3323,154 +3314,154 @@
   <dimension ref="A1:M21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="164"/>
+    <col min="1" max="1" width="9.140625" style="57"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="164" t="s">
+      <c r="A1" s="57" t="s">
         <v>101</v>
       </c>
       <c r="B1" t="s">
         <v>102</v>
       </c>
-      <c r="C1" s="165">
+      <c r="C1" s="58">
         <v>1</v>
       </c>
       <c r="D1" t="str">
         <f>Loans!C2</f>
         <v>Your Name Here</v>
       </c>
-      <c r="F1" s="166" t="str">
+      <c r="F1" s="124" t="str">
         <f ca="1">IF(M1="ACTIVE", "✓ Tracking Active", "⚠️ ERROR: Enable Iterative Calculations (File &gt; Options &gt; Formulas)")</f>
         <v>✓ Tracking Active</v>
       </c>
-      <c r="G1" s="166"/>
-      <c r="H1" s="166"/>
-      <c r="I1" s="166"/>
-      <c r="J1" s="166"/>
-      <c r="K1" s="166"/>
-      <c r="L1" s="166"/>
-      <c r="M1" s="164" t="str">
+      <c r="G1" s="124"/>
+      <c r="H1" s="124"/>
+      <c r="I1" s="124"/>
+      <c r="J1" s="124"/>
+      <c r="K1" s="124"/>
+      <c r="L1" s="124"/>
+      <c r="M1" s="57" t="str">
         <f ca="1">IF(M1="ACTIVE", "ACTIVE", "ACTIVE")</f>
         <v>ACTIVE</v>
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="164" t="str">
+      <c r="A2" s="57" t="str">
         <f t="shared" ref="A2:A19" ca="1" si="0">IF(D$1&lt;&gt;A3,A3,A2)</f>
         <v/>
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="164" t="str">
+      <c r="A3" s="57" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="164" t="str">
+      <c r="A4" s="57" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="164" t="str">
+      <c r="A5" s="57" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6" s="164" t="str">
+      <c r="A6" s="57" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
     <row r="7" spans="1:13">
-      <c r="A7" s="164" t="str">
+      <c r="A7" s="57" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="164" t="str">
+      <c r="A8" s="57" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="164" t="str">
+      <c r="A9" s="57" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="164" t="str">
+      <c r="A10" s="57" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
     <row r="11" spans="1:13">
-      <c r="A11" s="164" t="str">
+      <c r="A11" s="57" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
     <row r="12" spans="1:13">
-      <c r="A12" s="164" t="str">
+      <c r="A12" s="57" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
     <row r="13" spans="1:13">
-      <c r="A13" s="164" t="str">
+      <c r="A13" s="57" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
     <row r="14" spans="1:13">
-      <c r="A14" s="164" t="str">
+      <c r="A14" s="57" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" s="164" t="str">
+      <c r="A15" s="57" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="164" t="str">
+      <c r="A16" s="57" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="164" t="str">
+      <c r="A17" s="57" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="164" t="str">
+      <c r="A18" s="57" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="164" t="str">
+      <c r="A19" s="57" t="str">
         <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="164" t="str">
+      <c r="A20" s="57" t="str">
         <f ca="1">IF(D$1&lt;&gt;A21,A21,A20)</f>
         <v/>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="164" t="str">
+      <c r="A21" s="57" t="str">
         <f ca="1">IF(C1="","",IF(D$1&lt;&gt;A21,D$1,A21))</f>
         <v>Your Name Here</v>
       </c>
@@ -5529,10 +5520,10 @@
       <c r="I4" s="33"/>
     </row>
     <row r="5" spans="2:9" ht="16.5" thickTop="1">
-      <c r="B5" s="135" t="s">
+      <c r="B5" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="136"/>
+      <c r="C5" s="133"/>
       <c r="D5" s="33"/>
       <c r="E5" s="33"/>
       <c r="H5" s="33"/>
@@ -5600,36 +5591,36 @@
     </row>
     <row r="11" spans="2:9" ht="16.5" thickTop="1" thickBot="1"/>
     <row r="12" spans="2:9">
-      <c r="B12" s="137" t="s">
+      <c r="B12" s="134" t="s">
         <v>77</v>
       </c>
-      <c r="C12" s="138"/>
-      <c r="D12" s="138"/>
-      <c r="E12" s="138"/>
-      <c r="F12" s="139"/>
+      <c r="C12" s="135"/>
+      <c r="D12" s="135"/>
+      <c r="E12" s="135"/>
+      <c r="F12" s="136"/>
     </row>
     <row r="13" spans="2:9" ht="15.75" thickBot="1">
-      <c r="B13" s="140"/>
-      <c r="C13" s="141"/>
-      <c r="D13" s="141"/>
-      <c r="E13" s="141"/>
-      <c r="F13" s="142"/>
+      <c r="B13" s="137"/>
+      <c r="C13" s="138"/>
+      <c r="D13" s="138"/>
+      <c r="E13" s="138"/>
+      <c r="F13" s="139"/>
     </row>
     <row r="14" spans="2:9" ht="16.899999999999999" customHeight="1">
-      <c r="B14" s="143" t="s">
+      <c r="B14" s="140" t="s">
         <v>78</v>
       </c>
-      <c r="C14" s="144"/>
-      <c r="D14" s="144"/>
-      <c r="E14" s="144"/>
-      <c r="F14" s="145"/>
+      <c r="C14" s="141"/>
+      <c r="D14" s="141"/>
+      <c r="E14" s="141"/>
+      <c r="F14" s="142"/>
     </row>
     <row r="15" spans="2:9" ht="16.899999999999999" customHeight="1" thickBot="1">
-      <c r="B15" s="146"/>
-      <c r="C15" s="147"/>
-      <c r="D15" s="147"/>
-      <c r="E15" s="147"/>
-      <c r="F15" s="148"/>
+      <c r="B15" s="143"/>
+      <c r="C15" s="144"/>
+      <c r="D15" s="144"/>
+      <c r="E15" s="144"/>
+      <c r="F15" s="145"/>
     </row>
     <row r="16" spans="2:9">
       <c r="B16" s="43" t="s">
@@ -5644,16 +5635,16 @@
       <c r="E16" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="F16" s="149" t="s">
+      <c r="F16" s="146" t="s">
         <v>26</v>
       </c>
-      <c r="G16" s="149" t="s">
+      <c r="G16" s="146" t="s">
         <v>27</v>
       </c>
-      <c r="H16" s="129" t="s">
+      <c r="H16" s="154" t="s">
         <v>28</v>
       </c>
-      <c r="I16" s="131"/>
+      <c r="I16" s="156"/>
     </row>
     <row r="17" spans="2:10">
       <c r="B17" s="45">
@@ -5671,20 +5662,20 @@
         <f ca="1">Random!H20</f>
         <v>5</v>
       </c>
-      <c r="F17" s="150"/>
-      <c r="G17" s="150"/>
-      <c r="H17" s="130"/>
-      <c r="I17" s="131"/>
+      <c r="F17" s="147"/>
+      <c r="G17" s="147"/>
+      <c r="H17" s="155"/>
+      <c r="I17" s="156"/>
     </row>
     <row r="18" spans="2:10" ht="14.45" customHeight="1">
-      <c r="B18" s="122" t="s">
+      <c r="B18" s="148" t="s">
         <v>81</v>
       </c>
-      <c r="C18" s="123"/>
-      <c r="D18" s="123"/>
-      <c r="E18" s="124"/>
-      <c r="F18" s="128"/>
-      <c r="G18" s="151" t="s">
+      <c r="C18" s="149"/>
+      <c r="D18" s="149"/>
+      <c r="E18" s="150"/>
+      <c r="F18" s="126"/>
+      <c r="G18" s="125" t="s">
         <v>82</v>
       </c>
       <c r="H18" s="48" t="s">
@@ -5696,12 +5687,12 @@
       <c r="J18" s="50"/>
     </row>
     <row r="19" spans="2:10">
-      <c r="B19" s="122"/>
-      <c r="C19" s="123"/>
-      <c r="D19" s="123"/>
-      <c r="E19" s="124"/>
-      <c r="F19" s="128"/>
-      <c r="G19" s="151"/>
+      <c r="B19" s="148"/>
+      <c r="C19" s="149"/>
+      <c r="D19" s="149"/>
+      <c r="E19" s="150"/>
+      <c r="F19" s="126"/>
+      <c r="G19" s="125"/>
       <c r="H19" s="51" t="e">
         <f>Loans!B17*(1+Loans!C17/Loans!D17)^(Loans!D17*Loans!E17)</f>
         <v>#DIV/0!</v>
@@ -5713,12 +5704,12 @@
       <c r="J19" s="50"/>
     </row>
     <row r="20" spans="2:10" ht="14.45" customHeight="1">
-      <c r="B20" s="122"/>
-      <c r="C20" s="123"/>
-      <c r="D20" s="123"/>
-      <c r="E20" s="124"/>
-      <c r="F20" s="128"/>
-      <c r="G20" s="151" t="s">
+      <c r="B20" s="148"/>
+      <c r="C20" s="149"/>
+      <c r="D20" s="149"/>
+      <c r="E20" s="150"/>
+      <c r="F20" s="126"/>
+      <c r="G20" s="125" t="s">
         <v>85</v>
       </c>
       <c r="H20" s="53" t="s">
@@ -5732,43 +5723,43 @@
       </c>
     </row>
     <row r="21" spans="2:10">
-      <c r="B21" s="122"/>
-      <c r="C21" s="123"/>
-      <c r="D21" s="123"/>
-      <c r="E21" s="124"/>
-      <c r="F21" s="128"/>
-      <c r="G21" s="151"/>
-      <c r="H21" s="132" t="e">
+      <c r="B21" s="148"/>
+      <c r="C21" s="149"/>
+      <c r="D21" s="149"/>
+      <c r="E21" s="150"/>
+      <c r="F21" s="126"/>
+      <c r="G21" s="125"/>
+      <c r="H21" s="157" t="e">
         <f>Loans!B17*((1+Loans!C17/Loans!D17)^(Loans!D17*Loans!E17)-1)/(Loans!C17/Loans!D17)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I21" s="133">
+      <c r="I21" s="129">
         <f>Loans!B17*Loans!D17*Loans!E17</f>
         <v>0</v>
       </c>
-      <c r="J21" s="133" t="e">
+      <c r="J21" s="129" t="e">
         <f>H21-I21</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="22" spans="2:10">
-      <c r="B22" s="122"/>
-      <c r="C22" s="123"/>
-      <c r="D22" s="123"/>
-      <c r="E22" s="124"/>
-      <c r="F22" s="128"/>
-      <c r="G22" s="151"/>
-      <c r="H22" s="132"/>
-      <c r="I22" s="134"/>
-      <c r="J22" s="134"/>
+      <c r="B22" s="148"/>
+      <c r="C22" s="149"/>
+      <c r="D22" s="149"/>
+      <c r="E22" s="150"/>
+      <c r="F22" s="126"/>
+      <c r="G22" s="125"/>
+      <c r="H22" s="157"/>
+      <c r="I22" s="130"/>
+      <c r="J22" s="130"/>
     </row>
     <row r="23" spans="2:10">
-      <c r="B23" s="122"/>
-      <c r="C23" s="123"/>
-      <c r="D23" s="123"/>
-      <c r="E23" s="124"/>
-      <c r="F23" s="128"/>
-      <c r="G23" s="151" t="s">
+      <c r="B23" s="148"/>
+      <c r="C23" s="149"/>
+      <c r="D23" s="149"/>
+      <c r="E23" s="150"/>
+      <c r="F23" s="126"/>
+      <c r="G23" s="125" t="s">
         <v>87</v>
       </c>
       <c r="H23" s="48" t="s">
@@ -5782,35 +5773,35 @@
       </c>
     </row>
     <row r="24" spans="2:10">
-      <c r="B24" s="122"/>
-      <c r="C24" s="123"/>
-      <c r="D24" s="123"/>
-      <c r="E24" s="124"/>
-      <c r="F24" s="128"/>
-      <c r="G24" s="151"/>
-      <c r="H24" s="132" t="e">
+      <c r="B24" s="148"/>
+      <c r="C24" s="149"/>
+      <c r="D24" s="149"/>
+      <c r="E24" s="150"/>
+      <c r="F24" s="126"/>
+      <c r="G24" s="125"/>
+      <c r="H24" s="157" t="e">
         <f>Loans!B17*(Loans!C17/Loans!D17)/(1-(1+Loans!C17/Loans!D17)^(-Loans!D17*Loans!E17))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I24" s="133">
+      <c r="I24" s="129">
         <f>Loans!D17*Loans!E17*Loans!H19</f>
         <v>0</v>
       </c>
-      <c r="J24" s="153">
+      <c r="J24" s="128">
         <f>I24-Loans!B17</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="2:10" ht="17.45" customHeight="1" thickBot="1">
-      <c r="B25" s="125"/>
-      <c r="C25" s="126"/>
-      <c r="D25" s="126"/>
-      <c r="E25" s="127"/>
-      <c r="F25" s="152"/>
-      <c r="G25" s="154"/>
-      <c r="H25" s="132"/>
-      <c r="I25" s="134"/>
-      <c r="J25" s="153"/>
+      <c r="B25" s="151"/>
+      <c r="C25" s="152"/>
+      <c r="D25" s="152"/>
+      <c r="E25" s="153"/>
+      <c r="F25" s="127"/>
+      <c r="G25" s="131"/>
+      <c r="H25" s="157"/>
+      <c r="I25" s="130"/>
+      <c r="J25" s="128"/>
     </row>
     <row r="26" spans="2:10">
       <c r="B26" s="54"/>
@@ -5827,14 +5818,6 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="K6FLfj/2GW8ZCTHv8p2xOh6RoXSFAt/EbNff2TRYiVEiR5k81I441LUk2VqjGrBYfbxIzcyIabf7eIRPuVbGfw==" saltValue="gn8DjQ/CYqWIJUrkECcB7A==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="20">
-    <mergeCell ref="J24:J25"/>
-    <mergeCell ref="J21:J22"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B12:F13"/>
-    <mergeCell ref="B14:F15"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="G16:G17"/>
     <mergeCell ref="B18:E25"/>
     <mergeCell ref="F18:F19"/>
     <mergeCell ref="H16:H17"/>
@@ -5843,10 +5826,18 @@
     <mergeCell ref="I21:I22"/>
     <mergeCell ref="H24:H25"/>
     <mergeCell ref="I24:I25"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B12:F13"/>
+    <mergeCell ref="B14:F15"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="G16:G17"/>
     <mergeCell ref="G18:G19"/>
     <mergeCell ref="F20:F22"/>
     <mergeCell ref="G20:G22"/>
     <mergeCell ref="F23:F25"/>
+    <mergeCell ref="J24:J25"/>
+    <mergeCell ref="J21:J22"/>
+    <mergeCell ref="G23:G25"/>
   </mergeCells>
   <conditionalFormatting sqref="H18:H21">
     <cfRule type="expression" dxfId="1" priority="2">
@@ -5873,34 +5864,34 @@
   <sheetData>
     <row r="1" spans="2:6" ht="15.75" thickBot="1"/>
     <row r="2" spans="2:6">
-      <c r="B2" s="155" t="s">
+      <c r="B2" s="158" t="s">
         <v>91</v>
       </c>
-      <c r="C2" s="156"/>
-      <c r="D2" s="156"/>
-      <c r="E2" s="156"/>
-      <c r="F2" s="157"/>
+      <c r="C2" s="159"/>
+      <c r="D2" s="159"/>
+      <c r="E2" s="159"/>
+      <c r="F2" s="160"/>
     </row>
     <row r="3" spans="2:6">
-      <c r="B3" s="158"/>
-      <c r="C3" s="159"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="160"/>
+      <c r="B3" s="161"/>
+      <c r="C3" s="162"/>
+      <c r="D3" s="162"/>
+      <c r="E3" s="162"/>
+      <c r="F3" s="163"/>
     </row>
     <row r="4" spans="2:6">
-      <c r="B4" s="158"/>
-      <c r="C4" s="159"/>
-      <c r="D4" s="159"/>
-      <c r="E4" s="159"/>
-      <c r="F4" s="160"/>
+      <c r="B4" s="161"/>
+      <c r="C4" s="162"/>
+      <c r="D4" s="162"/>
+      <c r="E4" s="162"/>
+      <c r="F4" s="163"/>
     </row>
     <row r="5" spans="2:6" ht="15.75" thickBot="1">
-      <c r="B5" s="161"/>
-      <c r="C5" s="162"/>
-      <c r="D5" s="162"/>
-      <c r="E5" s="162"/>
-      <c r="F5" s="163"/>
+      <c r="B5" s="164"/>
+      <c r="C5" s="165"/>
+      <c r="D5" s="165"/>
+      <c r="E5" s="165"/>
+      <c r="F5" s="166"/>
     </row>
   </sheetData>
   <mergeCells count="1">
